--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_wmprob.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_wmprob.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -392,7 +393,7 @@
         <v>0.46134239435195923</v>
       </c>
       <c r="M4" s="0">
-        <v>0.46625009179115295</v>
+        <v>0.46625009179115296</v>
       </c>
       <c r="N4" s="0">
         <v>0.42565497756004333</v>
@@ -436,7 +437,7 @@
         <v>0.42393088340759277</v>
       </c>
       <c r="L5" s="0">
-        <v>0.40463897585868835</v>
+        <v>0.40463897585868836</v>
       </c>
       <c r="M5" s="0">
         <v>0.41835656762123108</v>
@@ -509,7 +510,7 @@
         <v>0.50485795736312866</v>
       </c>
       <c r="E7" s="0">
-        <v>0.45140445232391357</v>
+        <v>0.45140445232391358</v>
       </c>
       <c r="F7" s="0">
         <v>0.46935120224952698</v>
@@ -521,10 +522,10 @@
         <v>0.49311602115631104</v>
       </c>
       <c r="I7" s="0">
-        <v>0.47092729806900024</v>
+        <v>0.47092729806900025</v>
       </c>
       <c r="J7" s="0">
-        <v>0.47087478637695312</v>
+        <v>0.47087478637695313</v>
       </c>
       <c r="K7" s="0">
         <v>0.48044899106025696</v>
